--- a/Result/checksun_type/證券業.xlsx
+++ b/Result/checksun_type/證券業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>11.99</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>11.7</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>3296.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4034.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4034.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>5339.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>6817.86</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>6817.86</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-914.8305392231832</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>3296</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>3296.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>11.96</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>11.98</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>11.69</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>11.69</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>3706.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4349.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4349.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>6147.1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>6918.0</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>6918</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-862.5022823279633</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>3706</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>3706.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>11.94</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>11.99</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>11.68</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>11.68</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2421.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>5026.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>5026</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>7654.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7196.24</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7196.24</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-800.8725481087931</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2421</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2421.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>11.94</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>11.99</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>11.67</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>11.67</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>3970.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>6211.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>6211.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>8116.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7297.44</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7297.44</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-546.5489082203794</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>3970</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>3970.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>12.0</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>11.98</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>11.66</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>11.66</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>6781.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>6452.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>6452.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>8235.7</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>7432.0</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>7432</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-329.6741045147746</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>6781</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>6781.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>12.05</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>11.96</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>11.65</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>11.65</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>4869.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>6643.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>6643.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>8135.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>7459.36</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>7459.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-309.2574526312401</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>4869</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>4869.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>12.16</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>11.64</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>11.64</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>7089.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>7944.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>7944.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>8344.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>7438.08</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>7438.08</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-64.188755203646</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>7089</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>7089.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>12.23</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>11.63</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>11.63</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>8349.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>10282.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>10282</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>8313.7</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>7346.6</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>7346.6</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>50.34469666447512</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>8349</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>8349.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>12.21</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>11.91</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>11.62</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>11.62</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>5174.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>10022.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>10022</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>7973.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>7282.86</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>7282.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>77.16588873805995</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>5174</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>5174.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>12.17</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>11.88</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>11.6</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>7736.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>10019.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>10019</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>8244.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>7302.06</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>7302.06</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>452.9045242453922</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>7736</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>7736.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>12.09</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>11.85</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>11.59</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>11.59</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>11376.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>9627.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>9627.200000000001</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>8541.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>7290.86</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>7290.86</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>698.9988419613892</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>11376</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>11376.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>25.38</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>26.01</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>24.1</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>4056.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>3702.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>3702.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>9282.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>5715.78</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>5715.78</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-1246.137122810735</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>4056</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>4056.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>25.99</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>24.02</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>24.02</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>2071.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>3998.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>3998.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>10059.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>5709.12</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>5709.12</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-1150.109597865478</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>2071</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2071.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>25.26</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>25.94</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>23.94</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>23.94</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>5174.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>5947.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>5947.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>12135.6</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>5752.16</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>5752.16</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-759.1735051627747</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>5174</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>5174.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>25.48</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>25.89</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>23.84</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>23.84</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>2831.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>6683.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>6683.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>14272.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>5689.26</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>5689.26</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-506.0443189745256</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>2831</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2831.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>25.81</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>23.76</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>23.76</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>4381.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>11347.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>11347.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>14463.2</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>5680.46</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>5680.46</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>124.677529829205</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>4381</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>4381.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>26.27</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>25.74</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>23.66</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>25.74</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>23.66</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>5535.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>14861.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>14861.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>14555.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>5668.02</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>5668.02</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>855.1845449120628</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>5535</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>5535.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>26.73</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>25.69</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>23.56</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>23.56</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>11815.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>16120.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>16120.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>14874.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>5571.12</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>5571.12</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>1744.580832712141</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>11815</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>11815.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>27.06</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>25.64</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>23.47</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>8854.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>18324.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>18324</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>14463.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>5340.02</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>5340.02</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>2279.983356972538</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>8854</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>8854.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>27.04</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>25.49</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>23.34</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>23.34</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>26154.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>21861.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>21861.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>14601.4</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>5168.04</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>5168.04</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>3280.666128881225</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>26154</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>26154.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>26.92</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>25.32</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>23.22</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>23.22</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>21951.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>17578.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>17578.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>12486.9</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>4648.02</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>4648.02</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>2739.474869862162</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>21951</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>21951.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>26.57</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>25.08</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>23.06</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>23.06</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>11828.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>14250.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>14250</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>10760.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>4234.14</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>4234.14</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>2318.827540196997</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>11828</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>11828.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>18.32</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>18.65</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>18.78</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>18.78</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>92.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>111.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>111</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>137.2</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>82.6</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>82.59999999999999</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>10.05090031401868</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>92</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>18.32</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>18.67</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>18.79</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>18.79</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>150.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>118.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>118.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>130.0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>81.92</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>81.92</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>14.54044467495842</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>150</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>18.34</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>18.81</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>18.81</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>55.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>195.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>195.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>116.9</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>84.98</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>84.98</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>14.22049216648097</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>55</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,21 +11807,17 @@
           <t>18.42</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>18.73</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
+      <c r="AM27" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="AO27" t="inlineStr">
         <is>
           <t>18.82</t>
         </is>
       </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>18.82</t>
-        </is>
-      </c>
       <c r="AP27" t="inlineStr">
         <is>
           <t>-106.86</t>
@@ -12012,20 +11858,16 @@
           <t>202.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>199.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>199.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>113.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>85.46</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>85.45999999999999</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>23.43411386271029</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>202</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>202.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>18.54</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>18.76</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>18.84</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>18.84</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>56.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>167.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>167</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>95.7</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>84.44</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>84.44</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>20.00949793365537</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>56</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>18.63</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>18.78</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>18.85</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>18.85</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>129.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>163.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>163.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>98.3</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>0</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>30.0454216802321</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>129</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>18.73</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>18.81</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>18.86</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>537.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>141.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>141.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>92.9</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>0</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>35.48797625819057</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>537</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>537.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>18.82</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>18.83</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>18.86</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>75.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>38</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>43.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>0</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-1.718659211089836</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>75</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,21 +13957,17 @@
           <t>18.84</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
+      <c r="AM32" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="AO32" t="inlineStr">
         <is>
           <t>18.84</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>18.84</t>
-        </is>
-      </c>
       <c r="AP32" t="inlineStr">
         <is>
           <t>19.69</t>
@@ -14192,20 +14008,16 @@
           <t>38.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>26.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>26.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>37.4</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>0</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-5.30961490966579</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>38</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,21 +14387,17 @@
           <t>18.84</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
+      <c r="AM33" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="AO33" t="inlineStr">
         <is>
           <t>18.84</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>18.84</t>
-        </is>
-      </c>
       <c r="AP33" t="inlineStr">
         <is>
           <t>46.44</t>
@@ -14628,20 +14438,16 @@
           <t>38.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>24.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>39.4</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>0</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-6.285636803714794</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>38</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,21 +14817,17 @@
           <t>18.83</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
+      <c r="AM34" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="AO34" t="inlineStr">
         <is>
           <t>18.84</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>18.87</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>18.84</t>
-        </is>
-      </c>
       <c r="AP34" t="inlineStr">
         <is>
           <t>38.19</t>
@@ -15064,20 +14868,16 @@
           <t>20.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>33.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>33.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>0</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-7.455466766509275</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>20</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>12.65</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>12.73</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>12.86</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>12.86</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>5820.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>7362.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>7362.8</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>10336.5</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>17222.3</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>17222.3</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-1823.231260050394</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>5820</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>5820.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>12.6</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>12.74</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>12.87</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>12.87</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>5158.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>8269.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>8269.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>10898.1</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>17576.8</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>17576.8</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-1694.921108653589</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>5158</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>5158.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>12.58</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>12.75</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>12.88</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>12.88</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>4562.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>11781.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>11781.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>11823.4</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>18079.76</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>18079.76</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-1380.15942420624</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>4562</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>4562.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>12.58</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>12.76</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>12.89</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>12.89</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>10906.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>12703.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>12703.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>16182.7</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>18321.96</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>18321.96</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-817.3513241312321</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>10906</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>10906.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>12.63</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>12.77</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>12.89</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>12.89</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>10368.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>12282.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>12282.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>17804.6</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>19099.76</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>19099.76</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-663.8629195908197</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>10368</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>10368.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>12.67</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>12.78</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>12.89</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>12.89</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>10353.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>13310.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>13310.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>18028.9</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>19278.74</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>19278.74</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-363.2415231191299</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>10353</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>10353.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>12.76</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>12.89</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>12.89</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>22720.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>13526.8</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>13526.8</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>18375.8</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>19397.76</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>19397.76</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>80.79766909468162</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>22720</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>22720.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>12.81</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>12.81</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>12.88</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>12.88</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>9170.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>11865.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>11865</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>17138.3</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>19098.68</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>19098.68</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-612.7819730675401</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>9170</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>9170.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>12.8</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>12.81</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>12.87</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>12.87</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>8800.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>19662.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>19662</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>16649.3</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>19104.02</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>19104.02</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-129.9392485468707</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>8800</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>8800.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>12.84</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>12.81</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>12.86</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>12.86</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>15508.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>23327.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>23327</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>16867.0</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>19172.82</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>19172.82</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>604.1196167879025</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>15508</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>15508.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>12.83</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>12.85</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>12.85</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>11436.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>22747.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>22747.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>16693.1</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>19355.48</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>19355.48</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>912.4851523808684</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>11436</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>11436.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>10.41</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>10.67</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>10.86</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>10.86</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>4091.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>2999.4</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>2999.4</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>3684.4</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>3942.96</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>3942.96</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-86.85191201458338</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>4091</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>4091.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>10.38</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>10.7</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>10.87</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>10.87</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>2273.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>2837.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>2837</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>3615.7</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>4000.58</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>4000.58</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-171.3486691377166</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>2273</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>2273.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>10.39</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>10.72</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>10.88</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>10.88</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>2279.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>3510.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>3510.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>3645.2</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>4094.52</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>4094.52</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-91.15301255870327</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>2279</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>2279.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>10.44</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>10.76</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>10.9</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>4626.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>4078.2</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>4078.2</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>4058.4</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>4089.44</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>4089.44</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>26.02481871698365</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>4626</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>4626.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>10.53</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>10.79</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>10.91</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>10.91</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>1728.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>3662.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>3662.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>3835.8</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>4080.44</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>4080.44</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-58.97202298621278</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>1728</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>1728.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>10.59</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>10.81</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>10.92</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>10.92</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>3279.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>4369.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>4369.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>3894.9</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>4094.16</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>4094.16</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>132.2100611158717</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>3279</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>3279.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>10.69</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>10.84</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>10.93</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>10.93</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>5639.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>4394.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>4394.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>4144.9</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>4078.64</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>4078.64</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>234.4269647932824</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>5639</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>5639.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>10.74</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>10.86</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>10.94</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>10.94</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>5119.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>3780.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>3780.2</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>4011.8</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>3993.6</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>3993.6</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>119.2215784469668</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>5119</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>5119.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>10.75</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>10.88</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>10.94</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>10.94</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>2547.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>4038.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>4038.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>3663.9</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>3909.96</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>3909.96</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>6.098827293409158</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>2547</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>2547.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>10.78</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>10.94</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>10.94</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>5263.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>4009.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>4009.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>3608.1</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>3945.4</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>3945.4</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>119.8485103849912</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>5263</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>5263.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>10.8</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>10.95</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>10.95</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>3404.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>3420.4</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>3420.4</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>3402.4</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>3906.62</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>3906.62</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-12.93224628364214</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>3404</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>3404.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>25.07</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>24.62</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>24.63</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>24.63</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>107055545.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>145678973.6</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>145678973.6</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>146651119.0</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>146448893.5</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>146448893.5</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-1380934.643818647</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>107055545</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>107055545.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>24.88</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>24.6</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>122512502.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>140100793.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>140100793</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>149094092.0</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>150419442.2</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>150419442.2</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>1313129.181837291</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>122512502</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>122512502.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>24.66</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>24.57</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>24.57</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>119359614.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>147201156.8</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>147201156.8</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>146386404.3</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>153047615.34</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>153047615.34</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>3458791.783422977</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>119359614</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>119359614.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>24.57</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>24.62</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>24.53</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>24.53</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>150884153.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>147517632.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>147517632</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>150528422.9</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>154756386.36</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>154756386.36</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>6738305.221994609</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>150884153</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>150884153.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>24.59</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>24.63</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>24.49</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>24.49</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>228583054.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>182692466.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>182692466.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>146303961.8</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>153514896.52</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>153514896.52</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>7805041.483454287</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>228583054</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>228583054.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>24.51</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>24.44</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>24.44</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>79164642.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>147623264.4</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>147623264.4</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>131510149.0</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>151268652.1</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>151268652.1</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>725316.6968447119</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>79164642</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>79164642.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>24.57</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>24.68</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>24.4</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>158014321.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>158087391.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>158087391</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>136718498.3</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>152241067.1</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>152241067.1</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>6594635.548229456</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>158014321</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>158014321.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>24.61</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>24.73</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>24.36</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>24.73</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>24.36</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>120941990.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>145571651.8</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>145571651.8</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>128477026.0</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>150996048.68</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>150996048.68</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>6295674.173485219</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>120941990</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>120941990.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>24.62</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>24.74</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>24.3</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>24.3</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>326758324.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>153539213.8</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>153539213.8</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>122644713.3</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>150641880.76</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>150641880.76</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>9615776.453368992</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>326758324</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>326758324.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>24.54</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>24.74</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>24.24</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>24.24</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>53237045.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>109915457.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>109915457.4</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>101805951.4</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>146571242.86</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>146571242.86</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-8036390.948703155</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>53237045</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>53237045.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>24.46</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>24.73</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>24.18</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>24.73</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>24.18</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>131485275.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>115397033.6</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>115397033.6</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>117570731.1</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>148558101.28</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>148558101.28</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-3660907.667781085</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>131485275</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>131485275.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>15.01</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>15.66</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>15</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>12833.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>11086.4</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>11086.4</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>17179.0</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>22522.16</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>22522.16</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-3538.481107863328</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>12833</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>12833.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>14.99</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>15.72</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>14.98</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>14.98</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>10656.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>10932.2</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>10932.2</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>20750.0</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>22567.6</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>22567.6</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-3634.692135160749</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>10656</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>10656.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>15.01</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>15.76</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>14.96</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>11465.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>17381.8</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>17381.8</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>22629.3</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>22604.5</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>22604.5</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-3409.076026472747</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>11465</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>11465.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>15.17</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>15.8</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>14.94</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>14.94</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>11063.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>18663.0</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>18663</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>24853.1</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>22561.84</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>22561.84</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-3051.693155973007</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>11063</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>11063.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>15.41</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>15.81</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>14.92</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>9415.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>19260.2</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>19260.2</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>27721.0</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>22613.62</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>22613.62</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-2389.085728260052</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>9415</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>9415.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>15.62</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>15.8</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>14.9</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>14.9</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>12062.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>23271.6</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>23271.6</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>33521.4</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>22796.86</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>22796.86</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-1180.607769803693</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>12062</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>12062.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>15.92</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>15.82</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>14.88</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>14.88</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>42904.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>30567.8</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>30567.8</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>34209.1</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>22685.82</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>22685.82</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>304.3467340555253</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>42904</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>42904.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>16.06</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>15.8</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>14.86</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>14.86</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>17871.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>27876.8</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>27876.8</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>31589.8</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>22052.88</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>22052.88</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-889.659215219006</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>17871</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>17871.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>16.09</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>15.74</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>14.82</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>14.82</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>14049.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>31043.2</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>31043.2</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>31514.4</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>21972.88</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>21972.88</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>118.4986863609156</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>14049</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>14049.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>16.09</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>15.66</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>14.78</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>14.78</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>29472.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>36181.8</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>36181.8</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>34483.8</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>22124.06</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>22124.06</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>1963.992164105061</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>29472</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>29472.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>16.08</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>15.58</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>14.74</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>14.74</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>48543.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>43771.2</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>43771.2</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>35306.6</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>22047.68</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>22047.68</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>2877.804555021517</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>48543</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>48543.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>24.26</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>24.23</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>23.81</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>23.81</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>57172993.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>63840150.4</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>63840150.4</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>76623016.5</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>82957487.3</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>82957487.3</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-5251699.685185656</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>57172993</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>57172993.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>24.12</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>24.22</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>23.76</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>23.76</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>43929418.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>62293102.4</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>62293102.4</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>81886461.2</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>84195322.12</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>84195322.12</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-4587984.176249713</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>43929418</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>43929418.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>24.07</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>24.21</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>23.73</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>23.73</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>96621706.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>74217174.0</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>74217174</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>84716882.9</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>85188873.58</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>85188873.58</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-2057008.12147516</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>96621706</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>96621706.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>24.17</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>24.22</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>23.69</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>23.69</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>38705341.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>71276170.2</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>71276170.2</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>84514334.1</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>84983366.24</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>84983366.23999999</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-4013465.753173098</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>38705341</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>38705341.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>24.29</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>24.22</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>23.64</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>23.64</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>82771294.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>86915653.8</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>86915653.8</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>103710297.0</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>85153311.8</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>85153311.8</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-459742.3429853916</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>82771294</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>82771294.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>24.35</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>24.2</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>23.58</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>23.58</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>49437753.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>89405882.6</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>89405882.59999999</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>99507647.1</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>85182359.34</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>85182359.34</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-87927.35189633071</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>49437753</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>49437753.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>24.57</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>24.22</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>23.53</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>23.53</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>103549776.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>101479820.0</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>101479820</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>101577330.3</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>85289542.92</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>85289542.92</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>4017828.005084336</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>103549776</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>103549776.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>24.68</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>24.22</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>23.47</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>81916687.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>95216591.8</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>95216591.8</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>101011890.8</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>83699357.88</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>83699357.88</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>3941982.193446547</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>81916687</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>81916687.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>24.69</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>24.19</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>23.39</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>23.39</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>116902759.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>97752498.0</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>97752498</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>99246191.7</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>82707403.2</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>82707403.2</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>6010676.919912338</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>116902759</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>116902759.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>24.61</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>24.14</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>23.31</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>23.31</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>95222438.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>120504940.2</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>120504940.2</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>91503119.9</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>80910136.32</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>80910136.31999999</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>5002780.353438035</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>95222438</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>95222438.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>24.46</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>24.08</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>23.23</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>23.23</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>109807440.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>109609411.6</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>109609411.6</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>89574524.1</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>79894068.38</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>79894068.38</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>5707148.924423382</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>109807440</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>109807440.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>19.29</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>18.77</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>18.77</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>21024502.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>38763135.8</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>38763135.8</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>33598225.9</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>61887604.92</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>61887604.92</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-2796569.697427928</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>21024502</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>21024502.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>19.11</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>18.97</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>18.73</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>18.73</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>14261176.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>38554023.8</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>38554023.8</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>35215558.6</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>61954499.16</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>61954499.16</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-1834551.29628706</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>14261176</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>14261176.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>18.95</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>18.97</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>18.69</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>18.69</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>72153017.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>40891992.6</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>40891992.6</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>35353734.2</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>62233651.02</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>62233651.02</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>329922.4659244269</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>72153017</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>72153017.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>18.82</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>18.65</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>18.65</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>55038604.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>36667634.0</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>36667634</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>31486317.1</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>62020291.88</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>62020291.88</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-2792452.354699314</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>55038604</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>55038604.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>18.78</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>19.05</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>18.61</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>18.61</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>31338380.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>31167656.6</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>31167656.6</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>27002270.2</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>61076429.22</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>61076429.22</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-5319570.264351111</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>31338380</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>31338380.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>18.77</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>18.57</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>18.57</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>19978942.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>28433316.0</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>28433316</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>26651225.8</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>60651931.68</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>60651931.68</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-6200444.340126857</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>19978942</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>19978942.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>18.87</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>19.16</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>18.53</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>18.53</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>25951020.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>31877093.4</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>31877093.4</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>27161177.3</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>60538043.44</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>60538043.44</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-6020308.79337338</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>25951020</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>25951020.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>18.99</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>19.23</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>18.5</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>18.5</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>51031224.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>29815475.8</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>29815475.8</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>26393442.3</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>60291171.14</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>60291171.14</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-6187826.769676514</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>51031224</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>51031224.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>19.1</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>19.27</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>18.46</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>27538717.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>26305000.2</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>26305000.2</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>23543092.4</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>59600112.02</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>59600112.02</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>-8893309.065478258</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>27538717</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>27538717.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>19.12</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>18.42</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>18.42</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>17666677.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>22836883.8</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>22836883.8</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>24784393.7</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>59812865.1</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>59812865.1</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-9923611.27142796</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>17666677</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>17666677.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>19.16</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>18.37</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>18.37</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>37197829.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>24869135.6</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>24869135.6</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>28307567.2</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>60602850.02</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>60602850.02</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-9983338.30594796</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>37197829</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>37197829.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44035,11 +43441,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
           <t>2834</t>
@@ -44221,41 +43623,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
+      <c r="AM101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO101" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN101" t="inlineStr">
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT101" t="inlineStr">
         <is>
           <t>0</t>
@@ -44276,20 +43674,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>0</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>0</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43700,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>0</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43869,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44053,11 @@
           <t>21.06</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>21.36</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>21.96</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>21.96</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44104,16 @@
           <t>116282419.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>147052327.2</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>147052327.2</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>138102467.9</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>155068162.14</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>155068162.14</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44130,10 @@
           <t>1204165.073090315</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>116282419</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>116282419.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44299,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44483,11 @@
           <t>21.03</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>21.39</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>21.98</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>21.98</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44534,16 @@
           <t>94530656.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>154156015.4</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>154156015.4</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>136238579.6</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>156428624.36</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>156428624.36</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44560,10 @@
           <t>3769771.452193916</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>94530656</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>94530656.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44729,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44913,11 @@
           <t>21.04</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>21.99</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>21.99</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44964,16 @@
           <t>253863086.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>171154981.0</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>171154981</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>133468139.3</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>156046599.04</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>156046599.04</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44990,10 @@
           <t>9630834.76333502</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>253863086</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>253863086.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45159,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45343,11 @@
           <t>21.11</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>21.48</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>22.01</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>22.01</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45394,16 @@
           <t>153541023.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>149322704.2</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>149322704.2</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>117000702.8</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>152229876.58</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>152229876.58</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45420,10 @@
           <t>588492.1805603057</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>153541023</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>153541023.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45589,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45773,11 @@
           <t>21.21</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>21.53</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>22.02</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>22.02</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45824,16 @@
           <t>117044452.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>142327035.4</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>142327035.4</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>113627876.7</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>150846262.58</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>150846262.58</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45850,10 @@
           <t>-1601365.194137841</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>117044452</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>117044452.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46019,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46203,11 @@
           <t>21.28</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>21.57</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>22.03</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>22.03</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46254,16 @@
           <t>151800860.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>129152608.6</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>129152608.6</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>108888887.6</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>149915951.98</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>149915951.98</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46280,10 @@
           <t>-762194.3653445691</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>151800860</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>151800860.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46449,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46633,11 @@
           <t>21.38</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>21.64</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>22.04</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>22.04</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46684,16 @@
           <t>179525484.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>118321143.8</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>118321143.8</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>107889966.8</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>148811831.48</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>148811831.48</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46710,10 @@
           <t>-3260058.525449008</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>179525484</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>179525484.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46879,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47063,11 @@
           <t>21.48</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>22.05</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>22.05</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47114,16 @@
           <t>144701702.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>95781297.6</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>95781297.59999999</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>98681638.5</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>146653963.74</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>146653963.74</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47140,10 @@
           <t>-9682500.663975045</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>144701702</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>144701702.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47309,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47493,11 @@
           <t>21.52</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>22.05</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>22.05</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47544,16 @@
           <t>118562679.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>84678701.4</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>84678701.40000001</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>93476777.9</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>145151087.98</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>145151087.98</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47570,10 @@
           <t>-14780494.90958455</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>118562679</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>118562679.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47739,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47923,11 @@
           <t>21.56</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>22.05</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>22.05</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47974,16 @@
           <t>51172318.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>84928718.0</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>84928718</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>98125994.9</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>144492728.8</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>144492728.8</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48000,10 @@
           <t>-18734859.40654151</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>51172318</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>51172318.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48169,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48353,11 @@
           <t>21.59</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>21.82</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>22.05</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>22.05</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48404,16 @@
           <t>97643536.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>88625166.6</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>88625166.59999999</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>110514630.1</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>145223381.52</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>145223381.52</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48430,10 @@
           <t>-16494453.60196072</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>97643536</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>97643536.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
